--- a/data/datasheets/_templates/DataTemplateProcesses.xlsx
+++ b/data/datasheets/_templates/DataTemplateProcesses.xlsx
@@ -5,13 +5,14 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Information" sheetId="1" state="visible" r:id="rId2"/>
     <sheet name="description" sheetId="2" state="visible" r:id="rId3"/>
     <sheet name="flows" sheetId="3" state="visible" r:id="rId4"/>
-    <sheet name="supplementary" sheetId="4" state="visible" r:id="rId5"/>
+    <sheet name="transfer_coefficients" sheetId="4" state="visible" r:id="rId5"/>
+    <sheet name="supplementary" sheetId="5" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="55">
   <si>
     <t xml:space="preserve">This file contains the templates for the processes. Please fill in the information for each substance in the corresponding sheet.</t>
   </si>
@@ -49,6 +50,9 @@
     <t xml:space="preserve">material</t>
   </si>
   <si>
+    <t xml:space="preserve">x</t>
+  </si>
+  <si>
     <t xml:space="preserve">high</t>
   </si>
   <si>
@@ -106,6 +110,12 @@
     <t xml:space="preserve"> PARAMETERS</t>
   </si>
   <si>
+    <t xml:space="preserve">INPUT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OUTPUT</t>
+  </si>
+  <si>
     <t xml:space="preserve">UNIT</t>
   </si>
   <si>
@@ -164,6 +174,9 @@
   </si>
   <si>
     <t xml:space="preserve">Product 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transfer coefficients</t>
   </si>
   <si>
     <t xml:space="preserve">ADDITIONAL INFORMATION</t>
@@ -184,7 +197,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="&quot;TRUE&quot;;&quot;TRUE&quot;;&quot;FALSE&quot;"/>
   </numFmts>
   <fonts count="15">
     <font>
@@ -395,7 +408,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -416,11 +429,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -437,6 +450,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -476,23 +493,23 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="4" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="4" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -579,9 +596,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>29</xdr:col>
-      <xdr:colOff>53640</xdr:colOff>
+      <xdr:colOff>53280</xdr:colOff>
       <xdr:row>48</xdr:row>
-      <xdr:rowOff>153000</xdr:rowOff>
+      <xdr:rowOff>152640</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -595,7 +612,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="62280" y="891360"/>
-          <a:ext cx="17724960" cy="8504640"/>
+          <a:ext cx="17724600" cy="8504280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -675,22 +692,22 @@
       <c r="B1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="0"/>
-      <c r="D1" s="0"/>
-      <c r="E1" s="0"/>
-      <c r="F1" s="0"/>
-      <c r="G1" s="0"/>
-      <c r="H1" s="0"/>
-      <c r="I1" s="0"/>
-      <c r="J1" s="0"/>
-      <c r="K1" s="0"/>
-      <c r="L1" s="0"/>
-      <c r="M1" s="0"/>
-      <c r="N1" s="0"/>
-      <c r="O1" s="0"/>
-      <c r="P1" s="0"/>
-      <c r="Q1" s="0"/>
-      <c r="R1" s="0"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
+      <c r="P1" s="5"/>
+      <c r="Q1" s="5"/>
+      <c r="R1" s="5"/>
     </row>
     <row r="2" customFormat="false" ht="24.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
@@ -699,22 +716,22 @@
       <c r="B2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="0"/>
-      <c r="D2" s="0"/>
-      <c r="E2" s="0"/>
-      <c r="F2" s="0"/>
-      <c r="G2" s="0"/>
-      <c r="H2" s="0"/>
-      <c r="I2" s="0"/>
-      <c r="J2" s="0"/>
-      <c r="K2" s="0"/>
-      <c r="L2" s="0"/>
-      <c r="M2" s="0"/>
-      <c r="N2" s="0"/>
-      <c r="O2" s="0"/>
-      <c r="P2" s="0"/>
-      <c r="Q2" s="0"/>
-      <c r="R2" s="0"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
     </row>
     <row r="3" customFormat="false" ht="24.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
@@ -725,62 +742,80 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="24.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3"/>
+      <c r="A4" s="3" t="s">
+        <v>8</v>
+      </c>
       <c r="B4" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="24.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="24.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3"/>
       <c r="B5" s="4"/>
     </row>
     <row r="6" customFormat="false" ht="24.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3"/>
+      <c r="A6" s="3" t="s">
+        <v>8</v>
+      </c>
       <c r="B6" s="4"/>
     </row>
     <row r="7" customFormat="false" ht="24.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3"/>
+      <c r="A7" s="3" t="s">
+        <v>8</v>
+      </c>
       <c r="B7" s="4"/>
     </row>
     <row r="8" customFormat="false" ht="24.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3"/>
+      <c r="A8" s="3" t="s">
+        <v>8</v>
+      </c>
       <c r="B8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="24.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="24.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="24.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3"/>
+      <c r="A11" s="3" t="s">
+        <v>8</v>
+      </c>
       <c r="B11" s="4"/>
     </row>
     <row r="12" customFormat="false" ht="24.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3"/>
+      <c r="A12" s="3" t="s">
+        <v>8</v>
+      </c>
       <c r="B12" s="4"/>
     </row>
     <row r="13" customFormat="false" ht="24.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3"/>
+      <c r="A13" s="3" t="s">
+        <v>8</v>
+      </c>
       <c r="B13" s="4"/>
     </row>
     <row r="14" customFormat="false" ht="24.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3"/>
+      <c r="A14" s="3" t="s">
+        <v>8</v>
+      </c>
       <c r="B14" s="4"/>
     </row>
     <row r="15" customFormat="false" ht="24.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>5</v>
@@ -788,22 +823,24 @@
     </row>
     <row r="16" customFormat="false" ht="24.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="24.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="24.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3"/>
+      <c r="A18" s="3" t="s">
+        <v>8</v>
+      </c>
       <c r="B18" s="4"/>
     </row>
   </sheetData>
@@ -822,799 +859,841 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AF17"/>
+  <dimension ref="A1:AH17"/>
   <sheetFormatPr defaultColWidth="10.19921875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="5" width="27.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="6" width="19.47"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="6" width="25.32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="6" width="9.8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="7" width="7.08"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="7" width="7.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="6" width="27.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="7" width="19.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="7" width="25.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="7" width="9.8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="7" width="15.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="7" width="9.8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="7" width="7.08"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="7" width="7.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="7" width="7.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="7" width="7.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="7" width="7.08"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="7" width="7.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="7" width="7.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="7" width="7.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="7" width="7.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="7" width="7.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="7" width="7.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="7" width="7.08"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="7" width="7.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="7" width="7.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="7" width="7.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="7" width="7.08"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="7" width="7.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="7" width="7.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="7" width="7.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="7" width="7.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="7" width="7.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="7" width="7.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="7" width="7.08"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="7" width="7.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="7" width="7.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="7" width="7.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="7" width="7.08"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="7" width="7.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="7" width="7.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="7" width="7.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="7" width="7.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="7" width="7.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="7" width="7.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="7" width="7.08"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="7" width="7.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="7" width="7.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="7" width="7.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="7" width="36.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="31" min="30" style="7" width="39.96"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="32" min="32" style="7" width="50.32"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="33" style="7" width="10.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="7" width="7.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="7" width="7.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="7" width="7.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="7" width="7.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="30" style="7" width="7.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="31" min="31" style="7" width="36.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="32" style="7" width="39.97"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="34" min="34" style="7" width="50.32"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="35" style="7" width="10.2"/>
   </cols>
   <sheetData>
     <row r="1" s="8" customFormat="true" ht="30.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="5"/>
-      <c r="E1" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
+      <c r="A1" s="6"/>
+      <c r="G1" s="9" t="s">
+        <v>18</v>
+      </c>
       <c r="H1" s="9"/>
       <c r="I1" s="9"/>
       <c r="J1" s="9"/>
-      <c r="K1" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="10" t="s">
+        <v>19</v>
+      </c>
       <c r="N1" s="10"/>
       <c r="O1" s="10"/>
       <c r="P1" s="10"/>
-      <c r="Q1" s="10" t="s">
-        <v>19</v>
-      </c>
+      <c r="Q1" s="10"/>
       <c r="R1" s="10"/>
-      <c r="S1" s="10"/>
+      <c r="S1" s="10" t="s">
+        <v>20</v>
+      </c>
       <c r="T1" s="10"/>
       <c r="U1" s="10"/>
       <c r="V1" s="10"/>
-      <c r="W1" s="10" t="s">
-        <v>20</v>
-      </c>
+      <c r="W1" s="10"/>
       <c r="X1" s="10"/>
-      <c r="Y1" s="10"/>
+      <c r="Y1" s="10" t="s">
+        <v>21</v>
+      </c>
       <c r="Z1" s="10"/>
       <c r="AA1" s="10"/>
       <c r="AB1" s="10"/>
-      <c r="AC1" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="AD1" s="11"/>
+      <c r="AC1" s="10"/>
+      <c r="AD1" s="10"/>
       <c r="AE1" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="AF1" s="11" t="s">
+      <c r="AF1" s="11"/>
+      <c r="AG1" s="12" t="s">
         <v>23</v>
       </c>
+      <c r="AH1" s="12" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="2" s="8" customFormat="true" ht="56.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" s="13" t="s">
+      <c r="A2" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="B2" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="C2" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="E2" s="14" t="n">
+      <c r="D2" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" s="15" t="n">
         <v>2025</v>
       </c>
-      <c r="F2" s="14" t="n">
+      <c r="H2" s="15" t="n">
         <v>2030</v>
       </c>
-      <c r="G2" s="14" t="n">
+      <c r="I2" s="15" t="n">
         <v>2035</v>
       </c>
-      <c r="H2" s="14" t="n">
+      <c r="J2" s="15" t="n">
         <v>2040</v>
       </c>
-      <c r="I2" s="14" t="n">
+      <c r="K2" s="15" t="n">
         <v>2045</v>
       </c>
-      <c r="J2" s="14" t="n">
+      <c r="L2" s="15" t="n">
         <v>2050</v>
       </c>
-      <c r="K2" s="15" t="n">
+      <c r="M2" s="16" t="n">
         <v>2025</v>
       </c>
-      <c r="L2" s="16" t="n">
+      <c r="N2" s="17" t="n">
         <v>2030</v>
       </c>
-      <c r="M2" s="16" t="n">
+      <c r="O2" s="17" t="n">
         <v>2035</v>
       </c>
-      <c r="N2" s="16" t="n">
+      <c r="P2" s="17" t="n">
         <v>2040</v>
       </c>
-      <c r="O2" s="16" t="n">
+      <c r="Q2" s="17" t="n">
         <v>2045</v>
       </c>
-      <c r="P2" s="17" t="n">
+      <c r="R2" s="18" t="n">
         <v>2050</v>
       </c>
-      <c r="Q2" s="15" t="n">
+      <c r="S2" s="16" t="n">
         <v>2025</v>
       </c>
-      <c r="R2" s="16" t="n">
+      <c r="T2" s="17" t="n">
         <v>2030</v>
       </c>
-      <c r="S2" s="16" t="n">
+      <c r="U2" s="17" t="n">
         <v>2035</v>
       </c>
-      <c r="T2" s="16" t="n">
+      <c r="V2" s="17" t="n">
         <v>2040</v>
       </c>
-      <c r="U2" s="16" t="n">
+      <c r="W2" s="17" t="n">
         <v>2045</v>
       </c>
-      <c r="V2" s="17" t="n">
+      <c r="X2" s="18" t="n">
         <v>2050</v>
       </c>
-      <c r="W2" s="15" t="n">
+      <c r="Y2" s="16" t="n">
         <v>2025</v>
       </c>
-      <c r="X2" s="16" t="n">
+      <c r="Z2" s="17" t="n">
         <v>2030</v>
       </c>
-      <c r="Y2" s="16" t="n">
+      <c r="AA2" s="17" t="n">
         <v>2035</v>
       </c>
-      <c r="Z2" s="16" t="n">
+      <c r="AB2" s="17" t="n">
         <v>2040</v>
       </c>
-      <c r="AA2" s="16" t="n">
+      <c r="AC2" s="17" t="n">
         <v>2045</v>
       </c>
-      <c r="AB2" s="17" t="n">
+      <c r="AD2" s="18" t="n">
         <v>2050</v>
       </c>
-      <c r="AC2" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="AD2" s="8" t="s">
-        <v>28</v>
+      <c r="AE2" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="AF2" s="8" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="56.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="B3" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="C3" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="D3" s="19" t="s">
+      <c r="A3" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E3" s="20" t="n">
+      <c r="B3" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="E3" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="F3" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G3" s="22" t="n">
         <v>1.2</v>
       </c>
-      <c r="F3" s="20" t="n">
+      <c r="H3" s="22" t="n">
         <v>1.1</v>
       </c>
-      <c r="G3" s="20" t="n">
+      <c r="I3" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="H3" s="20" t="n">
+      <c r="J3" s="22" t="n">
         <v>0.9</v>
       </c>
-      <c r="I3" s="20" t="n">
+      <c r="K3" s="22" t="n">
         <v>0.8</v>
       </c>
-      <c r="J3" s="20" t="n">
+      <c r="L3" s="22" t="n">
         <v>0.7</v>
       </c>
-      <c r="K3" s="20" t="n">
-        <f aca="false">E3-0.1</f>
+      <c r="M3" s="22" t="n">
+        <f aca="false">G3-0.1</f>
         <v>1.1</v>
       </c>
-      <c r="L3" s="20" t="n">
-        <f aca="false">F3-0.1</f>
+      <c r="N3" s="22" t="n">
+        <f aca="false">H3-0.1</f>
         <v>1</v>
       </c>
-      <c r="M3" s="20" t="n">
-        <f aca="false">G3-0.1</f>
+      <c r="O3" s="22" t="n">
+        <f aca="false">I3-0.1</f>
         <v>0.9</v>
       </c>
-      <c r="N3" s="20" t="n">
-        <f aca="false">H3-0.1</f>
+      <c r="P3" s="22" t="n">
+        <f aca="false">J3-0.1</f>
         <v>0.8</v>
       </c>
-      <c r="O3" s="20" t="n">
-        <f aca="false">I3-0.1</f>
+      <c r="Q3" s="22" t="n">
+        <f aca="false">K3-0.1</f>
         <v>0.7</v>
       </c>
-      <c r="P3" s="20" t="n">
-        <f aca="false">J3-0.1</f>
+      <c r="R3" s="22" t="n">
+        <f aca="false">L3-0.1</f>
         <v>0.6</v>
       </c>
-      <c r="Q3" s="20" t="n">
-        <f aca="false">E3+0.1</f>
+      <c r="S3" s="22" t="n">
+        <f aca="false">G3+0.1</f>
         <v>1.3</v>
       </c>
-      <c r="R3" s="20" t="n">
-        <f aca="false">F3+0.1</f>
+      <c r="T3" s="22" t="n">
+        <f aca="false">H3+0.1</f>
         <v>1.2</v>
       </c>
-      <c r="S3" s="20" t="n">
-        <f aca="false">G3+0.1</f>
+      <c r="U3" s="22" t="n">
+        <f aca="false">I3+0.1</f>
         <v>1.1</v>
       </c>
-      <c r="T3" s="20" t="n">
-        <f aca="false">H3+0.1</f>
+      <c r="V3" s="22" t="n">
+        <f aca="false">J3+0.1</f>
         <v>1</v>
       </c>
-      <c r="U3" s="20" t="n">
-        <f aca="false">I3+0.1</f>
+      <c r="W3" s="22" t="n">
+        <f aca="false">K3+0.1</f>
         <v>0.9</v>
       </c>
-      <c r="V3" s="20" t="n">
-        <f aca="false">J3+0.1</f>
+      <c r="X3" s="22" t="n">
+        <f aca="false">L3+0.1</f>
         <v>0.8</v>
       </c>
-      <c r="W3" s="21" t="n">
+      <c r="Y3" s="20" t="n">
         <f aca="false">0.02</f>
         <v>0.02</v>
       </c>
-      <c r="X3" s="21" t="n">
+      <c r="Z3" s="20" t="n">
         <f aca="false">0.02</f>
         <v>0.02</v>
       </c>
-      <c r="Y3" s="21" t="n">
+      <c r="AA3" s="20" t="n">
         <f aca="false">0.02</f>
         <v>0.02</v>
       </c>
-      <c r="Z3" s="21" t="n">
+      <c r="AB3" s="20" t="n">
         <f aca="false">0.02</f>
         <v>0.02</v>
       </c>
-      <c r="AA3" s="21" t="n">
+      <c r="AC3" s="20" t="n">
         <f aca="false">0.02</f>
         <v>0.02</v>
       </c>
-      <c r="AB3" s="21" t="n">
+      <c r="AD3" s="20" t="n">
         <f aca="false">0.02</f>
         <v>0.02</v>
       </c>
-      <c r="AC3" s="21"/>
-      <c r="AD3" s="21"/>
-      <c r="AE3" s="21"/>
-      <c r="AF3" s="21"/>
+      <c r="AE3" s="20"/>
+      <c r="AF3" s="20"/>
+      <c r="AG3" s="20"/>
+      <c r="AH3" s="20"/>
     </row>
     <row r="4" customFormat="false" ht="56.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
+      <c r="A4" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
       <c r="E4" s="20"/>
       <c r="F4" s="20"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="20"/>
-      <c r="I4" s="20"/>
-      <c r="J4" s="20"/>
-      <c r="K4" s="20"/>
-      <c r="L4" s="20"/>
-      <c r="M4" s="20"/>
-      <c r="N4" s="20"/>
-      <c r="O4" s="20"/>
-      <c r="P4" s="20"/>
-      <c r="Q4" s="20"/>
-      <c r="R4" s="20"/>
-      <c r="S4" s="20"/>
-      <c r="T4" s="20"/>
-      <c r="U4" s="20"/>
-      <c r="V4" s="20"/>
-      <c r="W4" s="21"/>
-      <c r="X4" s="21"/>
-      <c r="Y4" s="21"/>
-      <c r="Z4" s="21"/>
-      <c r="AA4" s="21"/>
-      <c r="AB4" s="21"/>
-      <c r="AC4" s="21"/>
-      <c r="AD4" s="21"/>
-      <c r="AE4" s="21"/>
-      <c r="AF4" s="21"/>
+      <c r="G4" s="22"/>
+      <c r="H4" s="22"/>
+      <c r="I4" s="22"/>
+      <c r="J4" s="22"/>
+      <c r="K4" s="22"/>
+      <c r="L4" s="22"/>
+      <c r="M4" s="22"/>
+      <c r="N4" s="22"/>
+      <c r="O4" s="22"/>
+      <c r="P4" s="22"/>
+      <c r="Q4" s="22"/>
+      <c r="R4" s="22"/>
+      <c r="S4" s="22"/>
+      <c r="T4" s="22"/>
+      <c r="U4" s="22"/>
+      <c r="V4" s="22"/>
+      <c r="W4" s="22"/>
+      <c r="X4" s="22"/>
+      <c r="Y4" s="20"/>
+      <c r="Z4" s="20"/>
+      <c r="AA4" s="20"/>
+      <c r="AB4" s="20"/>
+      <c r="AC4" s="20"/>
+      <c r="AD4" s="20"/>
+      <c r="AE4" s="20"/>
+      <c r="AF4" s="20"/>
+      <c r="AG4" s="20"/>
+      <c r="AH4" s="20"/>
     </row>
     <row r="5" customFormat="false" ht="56.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="B5" s="19"/>
-      <c r="C5" s="19"/>
-      <c r="D5" s="19"/>
+      <c r="A5" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
       <c r="E5" s="20"/>
       <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="20"/>
-      <c r="J5" s="20"/>
-      <c r="K5" s="20"/>
-      <c r="L5" s="20"/>
-      <c r="M5" s="20"/>
-      <c r="N5" s="20"/>
-      <c r="O5" s="20"/>
-      <c r="P5" s="20"/>
-      <c r="Q5" s="20"/>
-      <c r="R5" s="20"/>
-      <c r="S5" s="20"/>
-      <c r="T5" s="20"/>
-      <c r="U5" s="20"/>
-      <c r="V5" s="20"/>
-      <c r="W5" s="21"/>
-      <c r="X5" s="21"/>
-      <c r="Y5" s="21"/>
-      <c r="Z5" s="21"/>
-      <c r="AA5" s="21"/>
-      <c r="AB5" s="21"/>
-      <c r="AC5" s="21"/>
-      <c r="AD5" s="21"/>
-      <c r="AE5" s="21"/>
-      <c r="AF5" s="21"/>
+      <c r="G5" s="22"/>
+      <c r="H5" s="22"/>
+      <c r="I5" s="22"/>
+      <c r="J5" s="22"/>
+      <c r="K5" s="22"/>
+      <c r="L5" s="22"/>
+      <c r="M5" s="22"/>
+      <c r="N5" s="22"/>
+      <c r="O5" s="22"/>
+      <c r="P5" s="22"/>
+      <c r="Q5" s="22"/>
+      <c r="R5" s="22"/>
+      <c r="S5" s="22"/>
+      <c r="T5" s="22"/>
+      <c r="U5" s="22"/>
+      <c r="V5" s="22"/>
+      <c r="W5" s="22"/>
+      <c r="X5" s="22"/>
+      <c r="Y5" s="20"/>
+      <c r="Z5" s="20"/>
+      <c r="AA5" s="20"/>
+      <c r="AB5" s="20"/>
+      <c r="AC5" s="20"/>
+      <c r="AD5" s="20"/>
+      <c r="AE5" s="20"/>
+      <c r="AF5" s="20"/>
+      <c r="AG5" s="20"/>
+      <c r="AH5" s="20"/>
     </row>
     <row r="6" customFormat="false" ht="56.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" s="19"/>
-      <c r="C6" s="19"/>
-      <c r="D6" s="19"/>
+      <c r="A6" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" s="20"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
       <c r="E6" s="20"/>
       <c r="F6" s="20"/>
-      <c r="G6" s="20"/>
-      <c r="H6" s="20"/>
-      <c r="I6" s="20"/>
-      <c r="J6" s="20"/>
-      <c r="K6" s="20"/>
-      <c r="L6" s="20"/>
-      <c r="M6" s="20"/>
-      <c r="N6" s="20"/>
-      <c r="O6" s="20"/>
-      <c r="P6" s="20"/>
-      <c r="Q6" s="20"/>
-      <c r="R6" s="20"/>
-      <c r="S6" s="20"/>
-      <c r="T6" s="20"/>
-      <c r="U6" s="20"/>
-      <c r="V6" s="20"/>
-      <c r="W6" s="21"/>
-      <c r="X6" s="21"/>
-      <c r="Y6" s="21"/>
-      <c r="Z6" s="21"/>
-      <c r="AA6" s="21"/>
-      <c r="AB6" s="21"/>
-      <c r="AC6" s="21"/>
-      <c r="AD6" s="21"/>
-      <c r="AE6" s="21"/>
-      <c r="AF6" s="21"/>
+      <c r="G6" s="22"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="22"/>
+      <c r="J6" s="22"/>
+      <c r="K6" s="22"/>
+      <c r="L6" s="22"/>
+      <c r="M6" s="22"/>
+      <c r="N6" s="22"/>
+      <c r="O6" s="22"/>
+      <c r="P6" s="22"/>
+      <c r="Q6" s="22"/>
+      <c r="R6" s="22"/>
+      <c r="S6" s="22"/>
+      <c r="T6" s="22"/>
+      <c r="U6" s="22"/>
+      <c r="V6" s="22"/>
+      <c r="W6" s="22"/>
+      <c r="X6" s="22"/>
+      <c r="Y6" s="20"/>
+      <c r="Z6" s="20"/>
+      <c r="AA6" s="20"/>
+      <c r="AB6" s="20"/>
+      <c r="AC6" s="20"/>
+      <c r="AD6" s="20"/>
+      <c r="AE6" s="20"/>
+      <c r="AF6" s="20"/>
+      <c r="AG6" s="20"/>
+      <c r="AH6" s="20"/>
     </row>
     <row r="7" customFormat="false" ht="56.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="B7" s="19"/>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19"/>
+      <c r="A7" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" s="20"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="20"/>
       <c r="E7" s="20"/>
       <c r="F7" s="20"/>
-      <c r="G7" s="20"/>
-      <c r="H7" s="20"/>
-      <c r="I7" s="20"/>
-      <c r="J7" s="20"/>
-      <c r="K7" s="20"/>
-      <c r="L7" s="20"/>
-      <c r="M7" s="20"/>
-      <c r="N7" s="20"/>
-      <c r="O7" s="20"/>
-      <c r="P7" s="20"/>
-      <c r="Q7" s="20"/>
-      <c r="R7" s="20"/>
-      <c r="S7" s="20"/>
-      <c r="T7" s="20"/>
-      <c r="U7" s="20"/>
-      <c r="V7" s="20"/>
-      <c r="W7" s="21"/>
-      <c r="X7" s="21"/>
-      <c r="Y7" s="21"/>
-      <c r="Z7" s="21"/>
-      <c r="AA7" s="21"/>
-      <c r="AB7" s="21"/>
-      <c r="AC7" s="21"/>
-      <c r="AD7" s="21"/>
-      <c r="AE7" s="21"/>
-      <c r="AF7" s="21"/>
+      <c r="G7" s="22"/>
+      <c r="H7" s="22"/>
+      <c r="I7" s="22"/>
+      <c r="J7" s="22"/>
+      <c r="K7" s="22"/>
+      <c r="L7" s="22"/>
+      <c r="M7" s="22"/>
+      <c r="N7" s="22"/>
+      <c r="O7" s="22"/>
+      <c r="P7" s="22"/>
+      <c r="Q7" s="22"/>
+      <c r="R7" s="22"/>
+      <c r="S7" s="22"/>
+      <c r="T7" s="22"/>
+      <c r="U7" s="22"/>
+      <c r="V7" s="22"/>
+      <c r="W7" s="22"/>
+      <c r="X7" s="22"/>
+      <c r="Y7" s="20"/>
+      <c r="Z7" s="20"/>
+      <c r="AA7" s="20"/>
+      <c r="AB7" s="20"/>
+      <c r="AC7" s="20"/>
+      <c r="AD7" s="20"/>
+      <c r="AE7" s="20"/>
+      <c r="AF7" s="20"/>
+      <c r="AG7" s="20"/>
+      <c r="AH7" s="20"/>
     </row>
     <row r="8" customFormat="false" ht="56.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="B8" s="19"/>
-      <c r="C8" s="19"/>
-      <c r="D8" s="19"/>
+      <c r="A8" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" s="20"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="20"/>
       <c r="E8" s="20"/>
       <c r="F8" s="20"/>
-      <c r="G8" s="20"/>
-      <c r="H8" s="20"/>
-      <c r="I8" s="20"/>
-      <c r="J8" s="20"/>
-      <c r="K8" s="20"/>
-      <c r="L8" s="20"/>
-      <c r="M8" s="20"/>
-      <c r="N8" s="20"/>
-      <c r="O8" s="20"/>
-      <c r="P8" s="20"/>
-      <c r="Q8" s="20"/>
-      <c r="R8" s="20"/>
-      <c r="S8" s="20"/>
-      <c r="T8" s="20"/>
-      <c r="U8" s="20"/>
-      <c r="V8" s="20"/>
-      <c r="W8" s="21"/>
-      <c r="X8" s="21"/>
-      <c r="Y8" s="21"/>
-      <c r="Z8" s="21"/>
-      <c r="AA8" s="21"/>
-      <c r="AB8" s="21"/>
-      <c r="AC8" s="21"/>
-      <c r="AD8" s="21"/>
-      <c r="AE8" s="21"/>
-      <c r="AF8" s="21"/>
+      <c r="G8" s="22"/>
+      <c r="H8" s="22"/>
+      <c r="I8" s="22"/>
+      <c r="J8" s="22"/>
+      <c r="K8" s="22"/>
+      <c r="L8" s="22"/>
+      <c r="M8" s="22"/>
+      <c r="N8" s="22"/>
+      <c r="O8" s="22"/>
+      <c r="P8" s="22"/>
+      <c r="Q8" s="22"/>
+      <c r="R8" s="22"/>
+      <c r="S8" s="22"/>
+      <c r="T8" s="22"/>
+      <c r="U8" s="22"/>
+      <c r="V8" s="22"/>
+      <c r="W8" s="22"/>
+      <c r="X8" s="22"/>
+      <c r="Y8" s="20"/>
+      <c r="Z8" s="20"/>
+      <c r="AA8" s="20"/>
+      <c r="AB8" s="20"/>
+      <c r="AC8" s="20"/>
+      <c r="AD8" s="20"/>
+      <c r="AE8" s="20"/>
+      <c r="AF8" s="20"/>
+      <c r="AG8" s="20"/>
+      <c r="AH8" s="20"/>
     </row>
     <row r="9" customFormat="false" ht="56.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" s="19"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19"/>
+      <c r="A9" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" s="20"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
       <c r="E9" s="20"/>
       <c r="F9" s="20"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="20"/>
-      <c r="I9" s="20"/>
-      <c r="J9" s="20"/>
-      <c r="K9" s="20"/>
-      <c r="L9" s="20"/>
-      <c r="M9" s="20"/>
-      <c r="N9" s="20"/>
-      <c r="O9" s="20"/>
-      <c r="P9" s="20"/>
-      <c r="Q9" s="20"/>
-      <c r="R9" s="20"/>
-      <c r="S9" s="20"/>
-      <c r="T9" s="20"/>
-      <c r="U9" s="20"/>
-      <c r="V9" s="20"/>
-      <c r="W9" s="21"/>
-      <c r="X9" s="21"/>
-      <c r="Y9" s="21"/>
-      <c r="Z9" s="21"/>
-      <c r="AA9" s="21"/>
-      <c r="AB9" s="21"/>
-      <c r="AC9" s="21"/>
-      <c r="AD9" s="21"/>
-      <c r="AE9" s="21"/>
-      <c r="AF9" s="21"/>
+      <c r="G9" s="22"/>
+      <c r="H9" s="22"/>
+      <c r="I9" s="22"/>
+      <c r="J9" s="22"/>
+      <c r="K9" s="22"/>
+      <c r="L9" s="22"/>
+      <c r="M9" s="22"/>
+      <c r="N9" s="22"/>
+      <c r="O9" s="22"/>
+      <c r="P9" s="22"/>
+      <c r="Q9" s="22"/>
+      <c r="R9" s="22"/>
+      <c r="S9" s="22"/>
+      <c r="T9" s="22"/>
+      <c r="U9" s="22"/>
+      <c r="V9" s="22"/>
+      <c r="W9" s="22"/>
+      <c r="X9" s="22"/>
+      <c r="Y9" s="20"/>
+      <c r="Z9" s="20"/>
+      <c r="AA9" s="20"/>
+      <c r="AB9" s="20"/>
+      <c r="AC9" s="20"/>
+      <c r="AD9" s="20"/>
+      <c r="AE9" s="20"/>
+      <c r="AF9" s="20"/>
+      <c r="AG9" s="20"/>
+      <c r="AH9" s="20"/>
     </row>
     <row r="10" customFormat="false" ht="56.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
+      <c r="A10" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" s="20"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
       <c r="E10" s="20"/>
       <c r="F10" s="20"/>
-      <c r="G10" s="20"/>
-      <c r="H10" s="20"/>
-      <c r="I10" s="20"/>
-      <c r="J10" s="20"/>
-      <c r="K10" s="20"/>
-      <c r="L10" s="20"/>
-      <c r="M10" s="20"/>
-      <c r="N10" s="20"/>
-      <c r="O10" s="20"/>
-      <c r="P10" s="20"/>
-      <c r="Q10" s="20"/>
-      <c r="R10" s="20"/>
-      <c r="S10" s="20"/>
-      <c r="T10" s="20"/>
-      <c r="U10" s="20"/>
-      <c r="V10" s="20"/>
-      <c r="W10" s="21"/>
-      <c r="X10" s="21"/>
-      <c r="Y10" s="21"/>
-      <c r="Z10" s="21"/>
-      <c r="AA10" s="21"/>
-      <c r="AB10" s="21"/>
-      <c r="AC10" s="21"/>
-      <c r="AD10" s="21"/>
-      <c r="AE10" s="21"/>
-      <c r="AF10" s="21"/>
+      <c r="G10" s="22"/>
+      <c r="H10" s="22"/>
+      <c r="I10" s="22"/>
+      <c r="J10" s="22"/>
+      <c r="K10" s="22"/>
+      <c r="L10" s="22"/>
+      <c r="M10" s="22"/>
+      <c r="N10" s="22"/>
+      <c r="O10" s="22"/>
+      <c r="P10" s="22"/>
+      <c r="Q10" s="22"/>
+      <c r="R10" s="22"/>
+      <c r="S10" s="22"/>
+      <c r="T10" s="22"/>
+      <c r="U10" s="22"/>
+      <c r="V10" s="22"/>
+      <c r="W10" s="22"/>
+      <c r="X10" s="22"/>
+      <c r="Y10" s="20"/>
+      <c r="Z10" s="20"/>
+      <c r="AA10" s="20"/>
+      <c r="AB10" s="20"/>
+      <c r="AC10" s="20"/>
+      <c r="AD10" s="20"/>
+      <c r="AE10" s="20"/>
+      <c r="AF10" s="20"/>
+      <c r="AG10" s="20"/>
+      <c r="AH10" s="20"/>
     </row>
     <row r="11" customFormat="false" ht="56.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="B11" s="19"/>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
+      <c r="A11" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
       <c r="E11" s="20"/>
       <c r="F11" s="20"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="20"/>
-      <c r="I11" s="20"/>
-      <c r="J11" s="20"/>
-      <c r="K11" s="20"/>
-      <c r="L11" s="20"/>
-      <c r="M11" s="20"/>
-      <c r="N11" s="20"/>
-      <c r="O11" s="20"/>
-      <c r="P11" s="20"/>
-      <c r="Q11" s="20"/>
-      <c r="R11" s="20"/>
-      <c r="S11" s="20"/>
-      <c r="T11" s="20"/>
-      <c r="U11" s="20"/>
-      <c r="V11" s="20"/>
-      <c r="W11" s="21"/>
-      <c r="X11" s="21"/>
-      <c r="Y11" s="21"/>
-      <c r="Z11" s="21"/>
-      <c r="AA11" s="21"/>
-      <c r="AB11" s="21"/>
-      <c r="AC11" s="21"/>
-      <c r="AD11" s="21"/>
-      <c r="AE11" s="21"/>
-      <c r="AF11" s="21"/>
+      <c r="G11" s="22"/>
+      <c r="H11" s="22"/>
+      <c r="I11" s="22"/>
+      <c r="J11" s="22"/>
+      <c r="K11" s="22"/>
+      <c r="L11" s="22"/>
+      <c r="M11" s="22"/>
+      <c r="N11" s="22"/>
+      <c r="O11" s="22"/>
+      <c r="P11" s="22"/>
+      <c r="Q11" s="22"/>
+      <c r="R11" s="22"/>
+      <c r="S11" s="22"/>
+      <c r="T11" s="22"/>
+      <c r="U11" s="22"/>
+      <c r="V11" s="22"/>
+      <c r="W11" s="22"/>
+      <c r="X11" s="22"/>
+      <c r="Y11" s="20"/>
+      <c r="Z11" s="20"/>
+      <c r="AA11" s="20"/>
+      <c r="AB11" s="20"/>
+      <c r="AC11" s="20"/>
+      <c r="AD11" s="20"/>
+      <c r="AE11" s="20"/>
+      <c r="AF11" s="20"/>
+      <c r="AG11" s="20"/>
+      <c r="AH11" s="20"/>
     </row>
     <row r="12" customFormat="false" ht="56.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
+      <c r="A12" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12" s="20"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
       <c r="E12" s="20"/>
       <c r="F12" s="20"/>
-      <c r="G12" s="20"/>
-      <c r="H12" s="20"/>
-      <c r="I12" s="20"/>
-      <c r="J12" s="20"/>
-      <c r="K12" s="20"/>
-      <c r="L12" s="20"/>
-      <c r="M12" s="20"/>
-      <c r="N12" s="20"/>
-      <c r="O12" s="20"/>
-      <c r="P12" s="20"/>
-      <c r="Q12" s="20"/>
-      <c r="R12" s="20"/>
-      <c r="S12" s="20"/>
-      <c r="T12" s="20"/>
-      <c r="U12" s="20"/>
-      <c r="V12" s="20"/>
-      <c r="W12" s="21"/>
-      <c r="X12" s="21"/>
-      <c r="Y12" s="21"/>
-      <c r="Z12" s="21"/>
-      <c r="AA12" s="21"/>
-      <c r="AB12" s="21"/>
-      <c r="AC12" s="21"/>
-      <c r="AD12" s="21"/>
-      <c r="AE12" s="21"/>
-      <c r="AF12" s="21"/>
+      <c r="G12" s="22"/>
+      <c r="H12" s="22"/>
+      <c r="I12" s="22"/>
+      <c r="J12" s="22"/>
+      <c r="K12" s="22"/>
+      <c r="L12" s="22"/>
+      <c r="M12" s="22"/>
+      <c r="N12" s="22"/>
+      <c r="O12" s="22"/>
+      <c r="P12" s="22"/>
+      <c r="Q12" s="22"/>
+      <c r="R12" s="22"/>
+      <c r="S12" s="22"/>
+      <c r="T12" s="22"/>
+      <c r="U12" s="22"/>
+      <c r="V12" s="22"/>
+      <c r="W12" s="22"/>
+      <c r="X12" s="22"/>
+      <c r="Y12" s="20"/>
+      <c r="Z12" s="20"/>
+      <c r="AA12" s="20"/>
+      <c r="AB12" s="20"/>
+      <c r="AC12" s="20"/>
+      <c r="AD12" s="20"/>
+      <c r="AE12" s="20"/>
+      <c r="AF12" s="20"/>
+      <c r="AG12" s="20"/>
+      <c r="AH12" s="20"/>
     </row>
     <row r="13" customFormat="false" ht="56.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
+      <c r="A13" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
       <c r="E13" s="20"/>
       <c r="F13" s="20"/>
-      <c r="G13" s="20"/>
-      <c r="H13" s="20"/>
-      <c r="I13" s="20"/>
-      <c r="J13" s="20"/>
-      <c r="K13" s="20"/>
-      <c r="L13" s="20"/>
-      <c r="M13" s="20"/>
-      <c r="N13" s="20"/>
-      <c r="O13" s="20"/>
-      <c r="P13" s="20"/>
-      <c r="Q13" s="20"/>
-      <c r="R13" s="20"/>
-      <c r="S13" s="20"/>
-      <c r="T13" s="20"/>
-      <c r="U13" s="20"/>
-      <c r="V13" s="20"/>
-      <c r="W13" s="21"/>
-      <c r="X13" s="21"/>
-      <c r="Y13" s="21"/>
-      <c r="Z13" s="21"/>
-      <c r="AA13" s="21"/>
-      <c r="AB13" s="21"/>
-      <c r="AC13" s="21"/>
-      <c r="AD13" s="21"/>
-      <c r="AE13" s="21"/>
-      <c r="AF13" s="21"/>
+      <c r="G13" s="22"/>
+      <c r="H13" s="22"/>
+      <c r="I13" s="22"/>
+      <c r="J13" s="22"/>
+      <c r="K13" s="22"/>
+      <c r="L13" s="22"/>
+      <c r="M13" s="22"/>
+      <c r="N13" s="22"/>
+      <c r="O13" s="22"/>
+      <c r="P13" s="22"/>
+      <c r="Q13" s="22"/>
+      <c r="R13" s="22"/>
+      <c r="S13" s="22"/>
+      <c r="T13" s="22"/>
+      <c r="U13" s="22"/>
+      <c r="V13" s="22"/>
+      <c r="W13" s="22"/>
+      <c r="X13" s="22"/>
+      <c r="Y13" s="20"/>
+      <c r="Z13" s="20"/>
+      <c r="AA13" s="20"/>
+      <c r="AB13" s="20"/>
+      <c r="AC13" s="20"/>
+      <c r="AD13" s="20"/>
+      <c r="AE13" s="20"/>
+      <c r="AF13" s="20"/>
+      <c r="AG13" s="20"/>
+      <c r="AH13" s="20"/>
     </row>
     <row r="14" customFormat="false" ht="56.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
+      <c r="A14" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
       <c r="E14" s="20"/>
       <c r="F14" s="20"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="20"/>
-      <c r="I14" s="20"/>
-      <c r="J14" s="20"/>
-      <c r="K14" s="20"/>
-      <c r="L14" s="20"/>
-      <c r="M14" s="20"/>
-      <c r="N14" s="20"/>
-      <c r="O14" s="20"/>
-      <c r="P14" s="20"/>
-      <c r="Q14" s="20"/>
-      <c r="R14" s="20"/>
-      <c r="S14" s="20"/>
-      <c r="T14" s="20"/>
-      <c r="U14" s="20"/>
-      <c r="V14" s="20"/>
-      <c r="W14" s="21"/>
-      <c r="X14" s="21"/>
-      <c r="Y14" s="21"/>
-      <c r="Z14" s="21"/>
-      <c r="AA14" s="21"/>
-      <c r="AB14" s="21"/>
-      <c r="AC14" s="21"/>
-      <c r="AD14" s="21"/>
-      <c r="AE14" s="21"/>
-      <c r="AF14" s="21"/>
+      <c r="G14" s="22"/>
+      <c r="H14" s="22"/>
+      <c r="I14" s="22"/>
+      <c r="J14" s="22"/>
+      <c r="K14" s="22"/>
+      <c r="L14" s="22"/>
+      <c r="M14" s="22"/>
+      <c r="N14" s="22"/>
+      <c r="O14" s="22"/>
+      <c r="P14" s="22"/>
+      <c r="Q14" s="22"/>
+      <c r="R14" s="22"/>
+      <c r="S14" s="22"/>
+      <c r="T14" s="22"/>
+      <c r="U14" s="22"/>
+      <c r="V14" s="22"/>
+      <c r="W14" s="22"/>
+      <c r="X14" s="22"/>
+      <c r="Y14" s="20"/>
+      <c r="Z14" s="20"/>
+      <c r="AA14" s="20"/>
+      <c r="AB14" s="20"/>
+      <c r="AC14" s="20"/>
+      <c r="AD14" s="20"/>
+      <c r="AE14" s="20"/>
+      <c r="AF14" s="20"/>
+      <c r="AG14" s="20"/>
+      <c r="AH14" s="20"/>
     </row>
     <row r="15" customFormat="false" ht="56.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="B15" s="19"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
+      <c r="A15" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
       <c r="E15" s="20"/>
       <c r="F15" s="20"/>
-      <c r="G15" s="20"/>
-      <c r="H15" s="20"/>
-      <c r="I15" s="20"/>
-      <c r="J15" s="20"/>
-      <c r="K15" s="20"/>
-      <c r="L15" s="20"/>
-      <c r="M15" s="20"/>
-      <c r="N15" s="20"/>
-      <c r="O15" s="20"/>
-      <c r="P15" s="20"/>
-      <c r="Q15" s="20"/>
-      <c r="R15" s="20"/>
-      <c r="S15" s="20"/>
-      <c r="T15" s="20"/>
-      <c r="U15" s="20"/>
-      <c r="V15" s="20"/>
-      <c r="W15" s="21"/>
-      <c r="X15" s="21"/>
-      <c r="Y15" s="21"/>
-      <c r="Z15" s="21"/>
-      <c r="AA15" s="21"/>
-      <c r="AB15" s="21"/>
-      <c r="AC15" s="21"/>
-      <c r="AD15" s="21"/>
-      <c r="AE15" s="21"/>
-      <c r="AF15" s="21"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="22"/>
+      <c r="I15" s="22"/>
+      <c r="J15" s="22"/>
+      <c r="K15" s="22"/>
+      <c r="L15" s="22"/>
+      <c r="M15" s="22"/>
+      <c r="N15" s="22"/>
+      <c r="O15" s="22"/>
+      <c r="P15" s="22"/>
+      <c r="Q15" s="22"/>
+      <c r="R15" s="22"/>
+      <c r="S15" s="22"/>
+      <c r="T15" s="22"/>
+      <c r="U15" s="22"/>
+      <c r="V15" s="22"/>
+      <c r="W15" s="22"/>
+      <c r="X15" s="22"/>
+      <c r="Y15" s="20"/>
+      <c r="Z15" s="20"/>
+      <c r="AA15" s="20"/>
+      <c r="AB15" s="20"/>
+      <c r="AC15" s="20"/>
+      <c r="AD15" s="20"/>
+      <c r="AE15" s="20"/>
+      <c r="AF15" s="20"/>
+      <c r="AG15" s="20"/>
+      <c r="AH15" s="20"/>
     </row>
     <row r="16" customFormat="false" ht="56.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="B16" s="19"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
+      <c r="A16" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="B16" s="20"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
       <c r="E16" s="20"/>
       <c r="F16" s="20"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="20"/>
-      <c r="I16" s="20"/>
-      <c r="J16" s="20"/>
-      <c r="K16" s="20"/>
-      <c r="L16" s="20"/>
-      <c r="M16" s="20"/>
-      <c r="N16" s="20"/>
-      <c r="O16" s="20"/>
-      <c r="P16" s="20"/>
-      <c r="Q16" s="20"/>
-      <c r="R16" s="20"/>
-      <c r="S16" s="20"/>
-      <c r="T16" s="20"/>
-      <c r="U16" s="20"/>
-      <c r="V16" s="20"/>
-      <c r="W16" s="21"/>
-      <c r="X16" s="21"/>
-      <c r="Y16" s="21"/>
-      <c r="Z16" s="21"/>
-      <c r="AA16" s="21"/>
-      <c r="AB16" s="21"/>
-      <c r="AC16" s="21"/>
-      <c r="AD16" s="21"/>
-      <c r="AE16" s="21"/>
-      <c r="AF16" s="21"/>
+      <c r="G16" s="22"/>
+      <c r="H16" s="22"/>
+      <c r="I16" s="22"/>
+      <c r="J16" s="22"/>
+      <c r="K16" s="22"/>
+      <c r="L16" s="22"/>
+      <c r="M16" s="22"/>
+      <c r="N16" s="22"/>
+      <c r="O16" s="22"/>
+      <c r="P16" s="22"/>
+      <c r="Q16" s="22"/>
+      <c r="R16" s="22"/>
+      <c r="S16" s="22"/>
+      <c r="T16" s="22"/>
+      <c r="U16" s="22"/>
+      <c r="V16" s="22"/>
+      <c r="W16" s="22"/>
+      <c r="X16" s="22"/>
+      <c r="Y16" s="20"/>
+      <c r="Z16" s="20"/>
+      <c r="AA16" s="20"/>
+      <c r="AB16" s="20"/>
+      <c r="AC16" s="20"/>
+      <c r="AD16" s="20"/>
+      <c r="AE16" s="20"/>
+      <c r="AF16" s="20"/>
+      <c r="AG16" s="20"/>
+      <c r="AH16" s="20"/>
     </row>
     <row r="17" customFormat="false" ht="56.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="B17" s="19"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="19"/>
+      <c r="A17" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="B17" s="20"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
       <c r="E17" s="20"/>
       <c r="F17" s="20"/>
-      <c r="G17" s="20"/>
-      <c r="H17" s="20"/>
-      <c r="I17" s="20"/>
-      <c r="J17" s="20"/>
-      <c r="K17" s="20"/>
-      <c r="L17" s="20"/>
-      <c r="M17" s="20"/>
-      <c r="N17" s="20"/>
-      <c r="O17" s="20"/>
-      <c r="P17" s="20"/>
-      <c r="Q17" s="20"/>
-      <c r="R17" s="20"/>
-      <c r="S17" s="20"/>
-      <c r="T17" s="20"/>
-      <c r="U17" s="20"/>
-      <c r="V17" s="20"/>
-      <c r="W17" s="21"/>
-      <c r="X17" s="21"/>
-      <c r="Y17" s="21"/>
-      <c r="Z17" s="21"/>
-      <c r="AA17" s="21"/>
-      <c r="AB17" s="21"/>
-      <c r="AC17" s="21"/>
-      <c r="AD17" s="21"/>
-      <c r="AE17" s="21"/>
-      <c r="AF17" s="21"/>
+      <c r="G17" s="22"/>
+      <c r="H17" s="22"/>
+      <c r="I17" s="22"/>
+      <c r="J17" s="22"/>
+      <c r="K17" s="22"/>
+      <c r="L17" s="22"/>
+      <c r="M17" s="22"/>
+      <c r="N17" s="22"/>
+      <c r="O17" s="22"/>
+      <c r="P17" s="22"/>
+      <c r="Q17" s="22"/>
+      <c r="R17" s="22"/>
+      <c r="S17" s="22"/>
+      <c r="T17" s="22"/>
+      <c r="U17" s="22"/>
+      <c r="V17" s="22"/>
+      <c r="W17" s="22"/>
+      <c r="X17" s="22"/>
+      <c r="Y17" s="20"/>
+      <c r="Z17" s="20"/>
+      <c r="AA17" s="20"/>
+      <c r="AB17" s="20"/>
+      <c r="AC17" s="20"/>
+      <c r="AD17" s="20"/>
+      <c r="AE17" s="20"/>
+      <c r="AF17" s="20"/>
+      <c r="AG17" s="20"/>
+      <c r="AH17" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="E1:J1"/>
-    <mergeCell ref="K1:P1"/>
-    <mergeCell ref="Q1:V1"/>
-    <mergeCell ref="W1:AB1"/>
-    <mergeCell ref="AC1:AD1"/>
+    <mergeCell ref="G1:L1"/>
+    <mergeCell ref="M1:R1"/>
+    <mergeCell ref="S1:X1"/>
+    <mergeCell ref="Y1:AD1"/>
+    <mergeCell ref="AE1:AF1"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -1631,133 +1710,989 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:AH17"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="6" width="27.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="7" width="19.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="7" width="25.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="7" width="9.8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="7" width="15.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="7" width="9.8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="7" width="7.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="7" width="7.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="7" width="7.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="7" width="7.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="7" width="7.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="7" width="7.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="7" width="7.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="7" width="7.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="7" width="7.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="7" width="7.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="7" width="7.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="7" width="7.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="7" width="7.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="7" width="7.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="7" width="7.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="7" width="7.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="7" width="7.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="7" width="7.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="7" width="7.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="7" width="7.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="7" width="7.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="7" width="7.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="7" width="7.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="30" style="7" width="7.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="31" min="31" style="7" width="36.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="32" style="7" width="39.97"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="34" min="34" style="7" width="50.32"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
+      <c r="J1" s="12"/>
+      <c r="K1" s="12"/>
+      <c r="L1" s="12"/>
+      <c r="M1" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="N1" s="10"/>
+      <c r="O1" s="10"/>
+      <c r="P1" s="10"/>
+      <c r="Q1" s="10"/>
+      <c r="R1" s="10"/>
+      <c r="S1" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="T1" s="10"/>
+      <c r="U1" s="10"/>
+      <c r="V1" s="10"/>
+      <c r="W1" s="10"/>
+      <c r="X1" s="10"/>
+      <c r="Y1" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="Z1" s="10"/>
+      <c r="AA1" s="10"/>
+      <c r="AB1" s="10"/>
+      <c r="AC1" s="10"/>
+      <c r="AD1" s="10"/>
+      <c r="AE1" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="AF1" s="11"/>
+      <c r="AG1" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="AH1" s="12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="56.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" s="15" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H2" s="15" t="n">
+        <v>2030</v>
+      </c>
+      <c r="I2" s="15" t="n">
+        <v>2035</v>
+      </c>
+      <c r="J2" s="15" t="n">
+        <v>2040</v>
+      </c>
+      <c r="K2" s="15" t="n">
+        <v>2045</v>
+      </c>
+      <c r="L2" s="15" t="n">
+        <v>2050</v>
+      </c>
+      <c r="M2" s="16" t="n">
+        <v>2025</v>
+      </c>
+      <c r="N2" s="17" t="n">
+        <v>2030</v>
+      </c>
+      <c r="O2" s="17" t="n">
+        <v>2035</v>
+      </c>
+      <c r="P2" s="17" t="n">
+        <v>2040</v>
+      </c>
+      <c r="Q2" s="17" t="n">
+        <v>2045</v>
+      </c>
+      <c r="R2" s="18" t="n">
+        <v>2050</v>
+      </c>
+      <c r="S2" s="16" t="n">
+        <v>2025</v>
+      </c>
+      <c r="T2" s="17" t="n">
+        <v>2030</v>
+      </c>
+      <c r="U2" s="17" t="n">
+        <v>2035</v>
+      </c>
+      <c r="V2" s="17" t="n">
+        <v>2040</v>
+      </c>
+      <c r="W2" s="17" t="n">
+        <v>2045</v>
+      </c>
+      <c r="X2" s="18" t="n">
+        <v>2050</v>
+      </c>
+      <c r="Y2" s="16" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Z2" s="17" t="n">
+        <v>2030</v>
+      </c>
+      <c r="AA2" s="17" t="n">
+        <v>2035</v>
+      </c>
+      <c r="AB2" s="17" t="n">
+        <v>2040</v>
+      </c>
+      <c r="AC2" s="17" t="n">
+        <v>2045</v>
+      </c>
+      <c r="AD2" s="18" t="n">
+        <v>2050</v>
+      </c>
+      <c r="AE2" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="AF2" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG2" s="8"/>
+      <c r="AH2" s="8"/>
+    </row>
+    <row r="3" customFormat="false" ht="56.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="E3" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="F3" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G3" s="22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H3" s="22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I3" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" s="22" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K3" s="22" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L3" s="22" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M3" s="22" t="n">
+        <f aca="false">G3-0.1</f>
+        <v>1.1</v>
+      </c>
+      <c r="N3" s="22" t="n">
+        <f aca="false">H3-0.1</f>
+        <v>1</v>
+      </c>
+      <c r="O3" s="22" t="n">
+        <f aca="false">I3-0.1</f>
+        <v>0.9</v>
+      </c>
+      <c r="P3" s="22" t="n">
+        <f aca="false">J3-0.1</f>
+        <v>0.8</v>
+      </c>
+      <c r="Q3" s="22" t="n">
+        <f aca="false">K3-0.1</f>
+        <v>0.7</v>
+      </c>
+      <c r="R3" s="22" t="n">
+        <f aca="false">L3-0.1</f>
+        <v>0.6</v>
+      </c>
+      <c r="S3" s="22" t="n">
+        <f aca="false">G3+0.1</f>
+        <v>1.3</v>
+      </c>
+      <c r="T3" s="22" t="n">
+        <f aca="false">H3+0.1</f>
+        <v>1.2</v>
+      </c>
+      <c r="U3" s="22" t="n">
+        <f aca="false">I3+0.1</f>
+        <v>1.1</v>
+      </c>
+      <c r="V3" s="22" t="n">
+        <f aca="false">J3+0.1</f>
+        <v>1</v>
+      </c>
+      <c r="W3" s="22" t="n">
+        <f aca="false">K3+0.1</f>
+        <v>0.9</v>
+      </c>
+      <c r="X3" s="22" t="n">
+        <f aca="false">L3+0.1</f>
+        <v>0.8</v>
+      </c>
+      <c r="Y3" s="20" t="n">
+        <f aca="false">0.02</f>
+        <v>0.02</v>
+      </c>
+      <c r="Z3" s="20" t="n">
+        <f aca="false">0.02</f>
+        <v>0.02</v>
+      </c>
+      <c r="AA3" s="20" t="n">
+        <f aca="false">0.02</f>
+        <v>0.02</v>
+      </c>
+      <c r="AB3" s="20" t="n">
+        <f aca="false">0.02</f>
+        <v>0.02</v>
+      </c>
+      <c r="AC3" s="20" t="n">
+        <f aca="false">0.02</f>
+        <v>0.02</v>
+      </c>
+      <c r="AD3" s="20" t="n">
+        <f aca="false">0.02</f>
+        <v>0.02</v>
+      </c>
+      <c r="AE3" s="20"/>
+      <c r="AF3" s="20"/>
+      <c r="AG3" s="20"/>
+      <c r="AH3" s="20"/>
+    </row>
+    <row r="4" customFormat="false" ht="56.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="22"/>
+      <c r="H4" s="22"/>
+      <c r="I4" s="22"/>
+      <c r="J4" s="22"/>
+      <c r="K4" s="22"/>
+      <c r="L4" s="22"/>
+      <c r="M4" s="22"/>
+      <c r="N4" s="22"/>
+      <c r="O4" s="22"/>
+      <c r="P4" s="22"/>
+      <c r="Q4" s="22"/>
+      <c r="R4" s="22"/>
+      <c r="S4" s="22"/>
+      <c r="T4" s="22"/>
+      <c r="U4" s="22"/>
+      <c r="V4" s="22"/>
+      <c r="W4" s="22"/>
+      <c r="X4" s="22"/>
+      <c r="Y4" s="20"/>
+      <c r="Z4" s="20"/>
+      <c r="AA4" s="20"/>
+      <c r="AB4" s="20"/>
+      <c r="AC4" s="20"/>
+      <c r="AD4" s="20"/>
+      <c r="AE4" s="20"/>
+      <c r="AF4" s="20"/>
+      <c r="AG4" s="20"/>
+      <c r="AH4" s="20"/>
+    </row>
+    <row r="5" customFormat="false" ht="56.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="22"/>
+      <c r="H5" s="22"/>
+      <c r="I5" s="22"/>
+      <c r="J5" s="22"/>
+      <c r="K5" s="22"/>
+      <c r="L5" s="22"/>
+      <c r="M5" s="22"/>
+      <c r="N5" s="22"/>
+      <c r="O5" s="22"/>
+      <c r="P5" s="22"/>
+      <c r="Q5" s="22"/>
+      <c r="R5" s="22"/>
+      <c r="S5" s="22"/>
+      <c r="T5" s="22"/>
+      <c r="U5" s="22"/>
+      <c r="V5" s="22"/>
+      <c r="W5" s="22"/>
+      <c r="X5" s="22"/>
+      <c r="Y5" s="20"/>
+      <c r="Z5" s="20"/>
+      <c r="AA5" s="20"/>
+      <c r="AB5" s="20"/>
+      <c r="AC5" s="20"/>
+      <c r="AD5" s="20"/>
+      <c r="AE5" s="20"/>
+      <c r="AF5" s="20"/>
+      <c r="AG5" s="20"/>
+      <c r="AH5" s="20"/>
+    </row>
+    <row r="6" customFormat="false" ht="56.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" s="20"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="22"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="22"/>
+      <c r="J6" s="22"/>
+      <c r="K6" s="22"/>
+      <c r="L6" s="22"/>
+      <c r="M6" s="22"/>
+      <c r="N6" s="22"/>
+      <c r="O6" s="22"/>
+      <c r="P6" s="22"/>
+      <c r="Q6" s="22"/>
+      <c r="R6" s="22"/>
+      <c r="S6" s="22"/>
+      <c r="T6" s="22"/>
+      <c r="U6" s="22"/>
+      <c r="V6" s="22"/>
+      <c r="W6" s="22"/>
+      <c r="X6" s="22"/>
+      <c r="Y6" s="20"/>
+      <c r="Z6" s="20"/>
+      <c r="AA6" s="20"/>
+      <c r="AB6" s="20"/>
+      <c r="AC6" s="20"/>
+      <c r="AD6" s="20"/>
+      <c r="AE6" s="20"/>
+      <c r="AF6" s="20"/>
+      <c r="AG6" s="20"/>
+      <c r="AH6" s="20"/>
+    </row>
+    <row r="7" customFormat="false" ht="56.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" s="20"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="20"/>
+      <c r="G7" s="22"/>
+      <c r="H7" s="22"/>
+      <c r="I7" s="22"/>
+      <c r="J7" s="22"/>
+      <c r="K7" s="22"/>
+      <c r="L7" s="22"/>
+      <c r="M7" s="22"/>
+      <c r="N7" s="22"/>
+      <c r="O7" s="22"/>
+      <c r="P7" s="22"/>
+      <c r="Q7" s="22"/>
+      <c r="R7" s="22"/>
+      <c r="S7" s="22"/>
+      <c r="T7" s="22"/>
+      <c r="U7" s="22"/>
+      <c r="V7" s="22"/>
+      <c r="W7" s="22"/>
+      <c r="X7" s="22"/>
+      <c r="Y7" s="20"/>
+      <c r="Z7" s="20"/>
+      <c r="AA7" s="20"/>
+      <c r="AB7" s="20"/>
+      <c r="AC7" s="20"/>
+      <c r="AD7" s="20"/>
+      <c r="AE7" s="20"/>
+      <c r="AF7" s="20"/>
+      <c r="AG7" s="20"/>
+      <c r="AH7" s="20"/>
+    </row>
+    <row r="8" customFormat="false" ht="56.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" s="20"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="20"/>
+      <c r="G8" s="22"/>
+      <c r="H8" s="22"/>
+      <c r="I8" s="22"/>
+      <c r="J8" s="22"/>
+      <c r="K8" s="22"/>
+      <c r="L8" s="22"/>
+      <c r="M8" s="22"/>
+      <c r="N8" s="22"/>
+      <c r="O8" s="22"/>
+      <c r="P8" s="22"/>
+      <c r="Q8" s="22"/>
+      <c r="R8" s="22"/>
+      <c r="S8" s="22"/>
+      <c r="T8" s="22"/>
+      <c r="U8" s="22"/>
+      <c r="V8" s="22"/>
+      <c r="W8" s="22"/>
+      <c r="X8" s="22"/>
+      <c r="Y8" s="20"/>
+      <c r="Z8" s="20"/>
+      <c r="AA8" s="20"/>
+      <c r="AB8" s="20"/>
+      <c r="AC8" s="20"/>
+      <c r="AD8" s="20"/>
+      <c r="AE8" s="20"/>
+      <c r="AF8" s="20"/>
+      <c r="AG8" s="20"/>
+      <c r="AH8" s="20"/>
+    </row>
+    <row r="9" customFormat="false" ht="56.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" s="20"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="22"/>
+      <c r="H9" s="22"/>
+      <c r="I9" s="22"/>
+      <c r="J9" s="22"/>
+      <c r="K9" s="22"/>
+      <c r="L9" s="22"/>
+      <c r="M9" s="22"/>
+      <c r="N9" s="22"/>
+      <c r="O9" s="22"/>
+      <c r="P9" s="22"/>
+      <c r="Q9" s="22"/>
+      <c r="R9" s="22"/>
+      <c r="S9" s="22"/>
+      <c r="T9" s="22"/>
+      <c r="U9" s="22"/>
+      <c r="V9" s="22"/>
+      <c r="W9" s="22"/>
+      <c r="X9" s="22"/>
+      <c r="Y9" s="20"/>
+      <c r="Z9" s="20"/>
+      <c r="AA9" s="20"/>
+      <c r="AB9" s="20"/>
+      <c r="AC9" s="20"/>
+      <c r="AD9" s="20"/>
+      <c r="AE9" s="20"/>
+      <c r="AF9" s="20"/>
+      <c r="AG9" s="20"/>
+      <c r="AH9" s="20"/>
+    </row>
+    <row r="10" customFormat="false" ht="56.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" s="20"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="22"/>
+      <c r="H10" s="22"/>
+      <c r="I10" s="22"/>
+      <c r="J10" s="22"/>
+      <c r="K10" s="22"/>
+      <c r="L10" s="22"/>
+      <c r="M10" s="22"/>
+      <c r="N10" s="22"/>
+      <c r="O10" s="22"/>
+      <c r="P10" s="22"/>
+      <c r="Q10" s="22"/>
+      <c r="R10" s="22"/>
+      <c r="S10" s="22"/>
+      <c r="T10" s="22"/>
+      <c r="U10" s="22"/>
+      <c r="V10" s="22"/>
+      <c r="W10" s="22"/>
+      <c r="X10" s="22"/>
+      <c r="Y10" s="20"/>
+      <c r="Z10" s="20"/>
+      <c r="AA10" s="20"/>
+      <c r="AB10" s="20"/>
+      <c r="AC10" s="20"/>
+      <c r="AD10" s="20"/>
+      <c r="AE10" s="20"/>
+      <c r="AF10" s="20"/>
+      <c r="AG10" s="20"/>
+      <c r="AH10" s="20"/>
+    </row>
+    <row r="11" customFormat="false" ht="56.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="20"/>
+      <c r="G11" s="22"/>
+      <c r="H11" s="22"/>
+      <c r="I11" s="22"/>
+      <c r="J11" s="22"/>
+      <c r="K11" s="22"/>
+      <c r="L11" s="22"/>
+      <c r="M11" s="22"/>
+      <c r="N11" s="22"/>
+      <c r="O11" s="22"/>
+      <c r="P11" s="22"/>
+      <c r="Q11" s="22"/>
+      <c r="R11" s="22"/>
+      <c r="S11" s="22"/>
+      <c r="T11" s="22"/>
+      <c r="U11" s="22"/>
+      <c r="V11" s="22"/>
+      <c r="W11" s="22"/>
+      <c r="X11" s="22"/>
+      <c r="Y11" s="20"/>
+      <c r="Z11" s="20"/>
+      <c r="AA11" s="20"/>
+      <c r="AB11" s="20"/>
+      <c r="AC11" s="20"/>
+      <c r="AD11" s="20"/>
+      <c r="AE11" s="20"/>
+      <c r="AF11" s="20"/>
+      <c r="AG11" s="20"/>
+      <c r="AH11" s="20"/>
+    </row>
+    <row r="12" customFormat="false" ht="56.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12" s="20"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="22"/>
+      <c r="H12" s="22"/>
+      <c r="I12" s="22"/>
+      <c r="J12" s="22"/>
+      <c r="K12" s="22"/>
+      <c r="L12" s="22"/>
+      <c r="M12" s="22"/>
+      <c r="N12" s="22"/>
+      <c r="O12" s="22"/>
+      <c r="P12" s="22"/>
+      <c r="Q12" s="22"/>
+      <c r="R12" s="22"/>
+      <c r="S12" s="22"/>
+      <c r="T12" s="22"/>
+      <c r="U12" s="22"/>
+      <c r="V12" s="22"/>
+      <c r="W12" s="22"/>
+      <c r="X12" s="22"/>
+      <c r="Y12" s="20"/>
+      <c r="Z12" s="20"/>
+      <c r="AA12" s="20"/>
+      <c r="AB12" s="20"/>
+      <c r="AC12" s="20"/>
+      <c r="AD12" s="20"/>
+      <c r="AE12" s="20"/>
+      <c r="AF12" s="20"/>
+      <c r="AG12" s="20"/>
+      <c r="AH12" s="20"/>
+    </row>
+    <row r="13" customFormat="false" ht="56.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="22"/>
+      <c r="H13" s="22"/>
+      <c r="I13" s="22"/>
+      <c r="J13" s="22"/>
+      <c r="K13" s="22"/>
+      <c r="L13" s="22"/>
+      <c r="M13" s="22"/>
+      <c r="N13" s="22"/>
+      <c r="O13" s="22"/>
+      <c r="P13" s="22"/>
+      <c r="Q13" s="22"/>
+      <c r="R13" s="22"/>
+      <c r="S13" s="22"/>
+      <c r="T13" s="22"/>
+      <c r="U13" s="22"/>
+      <c r="V13" s="22"/>
+      <c r="W13" s="22"/>
+      <c r="X13" s="22"/>
+      <c r="Y13" s="20"/>
+      <c r="Z13" s="20"/>
+      <c r="AA13" s="20"/>
+      <c r="AB13" s="20"/>
+      <c r="AC13" s="20"/>
+      <c r="AD13" s="20"/>
+      <c r="AE13" s="20"/>
+      <c r="AF13" s="20"/>
+      <c r="AG13" s="20"/>
+      <c r="AH13" s="20"/>
+    </row>
+    <row r="14" customFormat="false" ht="56.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="22"/>
+      <c r="H14" s="22"/>
+      <c r="I14" s="22"/>
+      <c r="J14" s="22"/>
+      <c r="K14" s="22"/>
+      <c r="L14" s="22"/>
+      <c r="M14" s="22"/>
+      <c r="N14" s="22"/>
+      <c r="O14" s="22"/>
+      <c r="P14" s="22"/>
+      <c r="Q14" s="22"/>
+      <c r="R14" s="22"/>
+      <c r="S14" s="22"/>
+      <c r="T14" s="22"/>
+      <c r="U14" s="22"/>
+      <c r="V14" s="22"/>
+      <c r="W14" s="22"/>
+      <c r="X14" s="22"/>
+      <c r="Y14" s="20"/>
+      <c r="Z14" s="20"/>
+      <c r="AA14" s="20"/>
+      <c r="AB14" s="20"/>
+      <c r="AC14" s="20"/>
+      <c r="AD14" s="20"/>
+      <c r="AE14" s="20"/>
+      <c r="AF14" s="20"/>
+      <c r="AG14" s="20"/>
+      <c r="AH14" s="20"/>
+    </row>
+    <row r="15" customFormat="false" ht="56.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="22"/>
+      <c r="I15" s="22"/>
+      <c r="J15" s="22"/>
+      <c r="K15" s="22"/>
+      <c r="L15" s="22"/>
+      <c r="M15" s="22"/>
+      <c r="N15" s="22"/>
+      <c r="O15" s="22"/>
+      <c r="P15" s="22"/>
+      <c r="Q15" s="22"/>
+      <c r="R15" s="22"/>
+      <c r="S15" s="22"/>
+      <c r="T15" s="22"/>
+      <c r="U15" s="22"/>
+      <c r="V15" s="22"/>
+      <c r="W15" s="22"/>
+      <c r="X15" s="22"/>
+      <c r="Y15" s="20"/>
+      <c r="Z15" s="20"/>
+      <c r="AA15" s="20"/>
+      <c r="AB15" s="20"/>
+      <c r="AC15" s="20"/>
+      <c r="AD15" s="20"/>
+      <c r="AE15" s="20"/>
+      <c r="AF15" s="20"/>
+      <c r="AG15" s="20"/>
+      <c r="AH15" s="20"/>
+    </row>
+    <row r="16" customFormat="false" ht="56.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="B16" s="20"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="22"/>
+      <c r="H16" s="22"/>
+      <c r="I16" s="22"/>
+      <c r="J16" s="22"/>
+      <c r="K16" s="22"/>
+      <c r="L16" s="22"/>
+      <c r="M16" s="22"/>
+      <c r="N16" s="22"/>
+      <c r="O16" s="22"/>
+      <c r="P16" s="22"/>
+      <c r="Q16" s="22"/>
+      <c r="R16" s="22"/>
+      <c r="S16" s="22"/>
+      <c r="T16" s="22"/>
+      <c r="U16" s="22"/>
+      <c r="V16" s="22"/>
+      <c r="W16" s="22"/>
+      <c r="X16" s="22"/>
+      <c r="Y16" s="20"/>
+      <c r="Z16" s="20"/>
+      <c r="AA16" s="20"/>
+      <c r="AB16" s="20"/>
+      <c r="AC16" s="20"/>
+      <c r="AD16" s="20"/>
+      <c r="AE16" s="20"/>
+      <c r="AF16" s="20"/>
+      <c r="AG16" s="20"/>
+      <c r="AH16" s="20"/>
+    </row>
+    <row r="17" customFormat="false" ht="56.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="B17" s="20"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="22"/>
+      <c r="H17" s="22"/>
+      <c r="I17" s="22"/>
+      <c r="J17" s="22"/>
+      <c r="K17" s="22"/>
+      <c r="L17" s="22"/>
+      <c r="M17" s="22"/>
+      <c r="N17" s="22"/>
+      <c r="O17" s="22"/>
+      <c r="P17" s="22"/>
+      <c r="Q17" s="22"/>
+      <c r="R17" s="22"/>
+      <c r="S17" s="22"/>
+      <c r="T17" s="22"/>
+      <c r="U17" s="22"/>
+      <c r="V17" s="22"/>
+      <c r="W17" s="22"/>
+      <c r="X17" s="22"/>
+      <c r="Y17" s="20"/>
+      <c r="Z17" s="20"/>
+      <c r="AA17" s="20"/>
+      <c r="AB17" s="20"/>
+      <c r="AC17" s="20"/>
+      <c r="AD17" s="20"/>
+      <c r="AE17" s="20"/>
+      <c r="AF17" s="20"/>
+      <c r="AG17" s="20"/>
+      <c r="AH17" s="20"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="F1:L1"/>
+    <mergeCell ref="M1:R1"/>
+    <mergeCell ref="S1:X1"/>
+    <mergeCell ref="Y1:AD1"/>
+    <mergeCell ref="AE1:AF1"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:S32"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="25.04"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="5" width="25.04"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="38.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="22" t="s">
-        <v>47</v>
-      </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
-      <c r="K1" s="22"/>
-      <c r="L1" s="22"/>
-      <c r="M1" s="22"/>
-      <c r="N1" s="22"/>
-      <c r="O1" s="22"/>
-      <c r="P1" s="22"/>
-      <c r="Q1" s="22"/>
-      <c r="R1" s="22"/>
-      <c r="S1" s="22"/>
+      <c r="A1" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+      <c r="M1" s="23"/>
+      <c r="N1" s="23"/>
+      <c r="O1" s="23"/>
+      <c r="P1" s="23"/>
+      <c r="Q1" s="23"/>
+      <c r="R1" s="23"/>
+      <c r="S1" s="23"/>
     </row>
     <row r="2" customFormat="false" ht="24.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="23"/>
+      <c r="A2" s="24"/>
     </row>
     <row r="3" customFormat="false" ht="24.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="23" t="s">
-        <v>48</v>
+      <c r="A3" s="24" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="24.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="23"/>
+      <c r="A4" s="24"/>
     </row>
     <row r="5" customFormat="false" ht="24.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="23"/>
+      <c r="A5" s="24"/>
     </row>
     <row r="6" customFormat="false" ht="24.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="23"/>
+      <c r="A6" s="24"/>
     </row>
     <row r="7" customFormat="false" ht="24.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="23"/>
+      <c r="A7" s="24"/>
     </row>
     <row r="8" customFormat="false" ht="24.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="23"/>
+      <c r="A8" s="24"/>
     </row>
     <row r="9" customFormat="false" ht="24.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="23"/>
+      <c r="A9" s="24"/>
     </row>
     <row r="10" customFormat="false" ht="24.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="23"/>
+      <c r="A10" s="24"/>
     </row>
     <row r="11" customFormat="false" ht="24.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="23"/>
+      <c r="A11" s="24"/>
     </row>
     <row r="12" customFormat="false" ht="24.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="23"/>
+      <c r="A12" s="24"/>
     </row>
     <row r="13" customFormat="false" ht="24.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="23" t="s">
-        <v>49</v>
+      <c r="A13" s="24" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="24.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="23"/>
+      <c r="A14" s="24"/>
     </row>
     <row r="15" customFormat="false" ht="24.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="23"/>
+      <c r="A15" s="24"/>
     </row>
     <row r="16" customFormat="false" ht="24.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="23"/>
+      <c r="A16" s="24"/>
     </row>
     <row r="17" customFormat="false" ht="24.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="23"/>
+      <c r="A17" s="24"/>
     </row>
     <row r="18" customFormat="false" ht="24.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="23"/>
+      <c r="A18" s="24"/>
     </row>
     <row r="19" customFormat="false" ht="24.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="23"/>
+      <c r="A19" s="24"/>
     </row>
     <row r="20" customFormat="false" ht="24.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="23" t="s">
-        <v>50</v>
+      <c r="A20" s="24" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="24.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="23"/>
+      <c r="A21" s="24"/>
     </row>
     <row r="22" customFormat="false" ht="24.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="23"/>
+      <c r="A22" s="24"/>
     </row>
     <row r="23" customFormat="false" ht="24.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="23"/>
+      <c r="A23" s="24"/>
     </row>
     <row r="24" customFormat="false" ht="24.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="23"/>
+      <c r="A24" s="24"/>
     </row>
     <row r="25" customFormat="false" ht="24.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="23"/>
+      <c r="A25" s="24"/>
     </row>
     <row r="26" customFormat="false" ht="24.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="23"/>
+      <c r="A26" s="24"/>
     </row>
     <row r="27" customFormat="false" ht="24.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="23"/>
+      <c r="A27" s="24"/>
     </row>
     <row r="28" customFormat="false" ht="24.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="23"/>
+      <c r="A28" s="24"/>
     </row>
     <row r="29" customFormat="false" ht="24.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="23"/>
+      <c r="A29" s="24"/>
     </row>
     <row r="30" customFormat="false" ht="24.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="23"/>
+      <c r="A30" s="24"/>
     </row>
     <row r="31" customFormat="false" ht="24.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="23"/>
+      <c r="A31" s="24"/>
     </row>
     <row r="32" customFormat="false" ht="24.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="24"/>
+      <c r="A32" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="1">
